--- a/assets/data/virtual_football_data.xlsx
+++ b/assets/data/virtual_football_data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1935" uniqueCount="260">
   <si>
     <t xml:space="preserve">code</t>
   </si>
@@ -27,97 +27,97 @@
     <t xml:space="preserve">PLY001</t>
   </si>
   <si>
-    <t xml:space="preserve">Real Madrid</t>
+    <t xml:space="preserve">Jugador 1</t>
   </si>
   <si>
     <t xml:space="preserve">PLY002</t>
   </si>
   <si>
-    <t xml:space="preserve">Manchester City</t>
+    <t xml:space="preserve">Jugador 2</t>
   </si>
   <si>
     <t xml:space="preserve">PLY003</t>
   </si>
   <si>
-    <t xml:space="preserve">Bayern Munich</t>
+    <t xml:space="preserve">Jugador 3</t>
   </si>
   <si>
     <t xml:space="preserve">PLY004</t>
   </si>
   <si>
-    <t xml:space="preserve">Chelsea</t>
+    <t xml:space="preserve">Jugador 4</t>
   </si>
   <si>
     <t xml:space="preserve">PLY005</t>
   </si>
   <si>
-    <t xml:space="preserve">Paris Saint-Germain</t>
+    <t xml:space="preserve">Jugador 5</t>
   </si>
   <si>
     <t xml:space="preserve">PLY006</t>
   </si>
   <si>
-    <t xml:space="preserve">Borussia Dortmund</t>
+    <t xml:space="preserve">Jugador 6</t>
   </si>
   <si>
     <t xml:space="preserve">PLY007</t>
   </si>
   <si>
-    <t xml:space="preserve">Inter Milan</t>
+    <t xml:space="preserve">Jugador 7</t>
   </si>
   <si>
     <t xml:space="preserve">PLY008</t>
   </si>
   <si>
-    <t xml:space="preserve">Liverpool</t>
+    <t xml:space="preserve">Jugador 8</t>
   </si>
   <si>
     <t xml:space="preserve">PLY009</t>
   </si>
   <si>
-    <t xml:space="preserve">Arsenal</t>
+    <t xml:space="preserve">Jugador 9</t>
   </si>
   <si>
     <t xml:space="preserve">PLY010</t>
   </si>
   <si>
-    <t xml:space="preserve">Barcelona</t>
+    <t xml:space="preserve">Jugador 10</t>
   </si>
   <si>
     <t xml:space="preserve">PLY011</t>
   </si>
   <si>
-    <t xml:space="preserve">Atletico Madrid</t>
+    <t xml:space="preserve">Jugador 11</t>
   </si>
   <si>
     <t xml:space="preserve">PLY012</t>
   </si>
   <si>
-    <t xml:space="preserve">Napoli</t>
+    <t xml:space="preserve">Jugador 12</t>
   </si>
   <si>
     <t xml:space="preserve">PLY013</t>
   </si>
   <si>
-    <t xml:space="preserve">Juventus</t>
+    <t xml:space="preserve">Jugador 13</t>
   </si>
   <si>
     <t xml:space="preserve">PLY014</t>
   </si>
   <si>
-    <t xml:space="preserve">AC Milan</t>
+    <t xml:space="preserve">Jugador 14</t>
   </si>
   <si>
     <t xml:space="preserve">PLY015</t>
   </si>
   <si>
-    <t xml:space="preserve">Benfica</t>
+    <t xml:space="preserve">Jugador 15</t>
   </si>
   <si>
     <t xml:space="preserve">PLY016</t>
   </si>
   <si>
-    <t xml:space="preserve">Porto</t>
+    <t xml:space="preserve">Jugador 16</t>
   </si>
   <si>
     <t xml:space="preserve">position</t>
@@ -330,6 +330,12 @@
     <t xml:space="preserve">schedule</t>
   </si>
   <si>
+    <t xml:space="preserve">startDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">endDate</t>
+  </si>
+  <si>
     <t xml:space="preserve">homeGoals</t>
   </si>
   <si>
@@ -342,21 +348,57 @@
     <t xml:space="preserve">CHP2020 MD1 21:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-04-10 21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-10 23:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHP2020 MD2 21:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-04-11 21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-11 23:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHP2020 MD3 21:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-04-12 21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-12 23:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHP2020 MD4 21:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-04-13 21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-13 23:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHP2020 MD5 21:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-04-14 21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-14 23:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHP2020 MD6 21:00</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-04-15 21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 23:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">Grupo B</t>
   </si>
   <si>
@@ -372,46 +414,136 @@
     <t xml:space="preserve">CHP2020 Octavos 1</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-05-01 20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-01 22:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHP2020 Octavos 2</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-05-02 20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-02 22:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHP2020 Octavos 3</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-05-03 20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-03 22:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHP2020 Octavos 4</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-05-04 20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-04 22:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHP2020 Octavos 5</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-05-05 20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-05 22:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHP2020 Octavos 6</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-05-06 20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-06 22:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHP2020 Octavos 7</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-05-07 20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-07 22:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHP2020 Octavos 8</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-05-08 20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-08 22:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHP2020 Cuartos 1</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-05-11 20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-11 22:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHP2020 Cuartos 2</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-05-12 20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-12 22:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHP2020 Cuartos 3</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-05-13 20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-13 22:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHP2020 Cuartos 4</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-05-14 20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-14 22:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHP2020 Semifinal 1</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-05-20 20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20 22:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHP2020 Semifinal 2</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-05-21 20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21 22:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHP2020 Final 21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28 21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28 23:00</t>
   </si>
   <si>
     <t xml:space="preserve">CHP2021 MD1 21:00</t>
@@ -4473,6 +4605,12 @@
       <c r="H1" s="1" t="s">
         <v>105</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
@@ -4482,7 +4620,7 @@
         <v>61</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>2</v>
@@ -4491,12 +4629,18 @@
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G2" s="2">
-        <v>2</v>
-      </c>
-      <c r="H2" s="2">
+        <v>109</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I2" s="2">
+        <v>2</v>
+      </c>
+      <c r="J2" s="2">
         <v>2</v>
       </c>
     </row>
@@ -4508,7 +4652,7 @@
         <v>61</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>2</v>
@@ -4517,12 +4661,18 @@
         <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2">
+        <v>112</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2">
         <v>3</v>
       </c>
     </row>
@@ -4534,7 +4684,7 @@
         <v>61</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>2</v>
@@ -4543,12 +4693,18 @@
         <v>32</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G4" s="2">
-        <v>2</v>
-      </c>
-      <c r="H4" s="2">
+        <v>115</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I4" s="2">
+        <v>2</v>
+      </c>
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4560,7 +4716,7 @@
         <v>61</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
@@ -4569,12 +4725,18 @@
         <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G5" s="2">
-        <v>3</v>
-      </c>
-      <c r="H5" s="2">
+        <v>118</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I5" s="2">
+        <v>3</v>
+      </c>
+      <c r="J5" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4586,7 +4748,7 @@
         <v>61</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
@@ -4595,12 +4757,18 @@
         <v>32</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2">
+        <v>121</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
         <v>2</v>
       </c>
     </row>
@@ -4612,7 +4780,7 @@
         <v>61</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>12</v>
@@ -4621,12 +4789,18 @@
         <v>32</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G7" s="2">
-        <v>3</v>
-      </c>
-      <c r="H7" s="2">
+        <v>124</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I7" s="2">
+        <v>3</v>
+      </c>
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4638,7 +4812,7 @@
         <v>61</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>4</v>
@@ -4647,12 +4821,18 @@
         <v>14</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G8" s="2">
-        <v>2</v>
-      </c>
-      <c r="H8" s="2">
+        <v>109</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I8" s="2">
+        <v>2</v>
+      </c>
+      <c r="J8" s="2">
         <v>2</v>
       </c>
     </row>
@@ -4664,7 +4844,7 @@
         <v>61</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>4</v>
@@ -4673,12 +4853,18 @@
         <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2">
+        <v>112</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
         <v>3</v>
       </c>
     </row>
@@ -4690,7 +4876,7 @@
         <v>61</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>4</v>
@@ -4699,12 +4885,18 @@
         <v>26</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G10" s="2">
-        <v>2</v>
-      </c>
-      <c r="H10" s="2">
+        <v>115</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I10" s="2">
+        <v>2</v>
+      </c>
+      <c r="J10" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4716,7 +4908,7 @@
         <v>61</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>14</v>
@@ -4725,12 +4917,18 @@
         <v>8</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G11" s="2">
-        <v>3</v>
-      </c>
-      <c r="H11" s="2">
+        <v>118</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I11" s="2">
+        <v>3</v>
+      </c>
+      <c r="J11" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4742,7 +4940,7 @@
         <v>61</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>14</v>
@@ -4751,12 +4949,18 @@
         <v>26</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G12" s="2">
-        <v>1</v>
-      </c>
-      <c r="H12" s="2">
+        <v>121</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2">
         <v>2</v>
       </c>
     </row>
@@ -4768,7 +4972,7 @@
         <v>61</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>8</v>
@@ -4777,12 +4981,18 @@
         <v>26</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G13" s="2">
-        <v>3</v>
-      </c>
-      <c r="H13" s="2">
+        <v>124</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I13" s="2">
+        <v>3</v>
+      </c>
+      <c r="J13" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4794,7 +5004,7 @@
         <v>61</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>6</v>
@@ -4803,12 +5013,18 @@
         <v>18</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G14" s="2">
-        <v>2</v>
-      </c>
-      <c r="H14" s="2">
+        <v>109</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I14" s="2">
+        <v>2</v>
+      </c>
+      <c r="J14" s="2">
         <v>2</v>
       </c>
     </row>
@@ -4820,7 +5036,7 @@
         <v>61</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>6</v>
@@ -4829,12 +5045,18 @@
         <v>20</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2">
+        <v>112</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
         <v>3</v>
       </c>
     </row>
@@ -4846,7 +5068,7 @@
         <v>61</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>6</v>
@@ -4855,12 +5077,18 @@
         <v>30</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G16" s="2">
-        <v>2</v>
-      </c>
-      <c r="H16" s="2">
+        <v>115</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I16" s="2">
+        <v>2</v>
+      </c>
+      <c r="J16" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4872,7 +5100,7 @@
         <v>61</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>18</v>
@@ -4881,12 +5109,18 @@
         <v>20</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G17" s="2">
-        <v>3</v>
-      </c>
-      <c r="H17" s="2">
+        <v>118</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I17" s="2">
+        <v>3</v>
+      </c>
+      <c r="J17" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4898,7 +5132,7 @@
         <v>61</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>18</v>
@@ -4907,12 +5141,18 @@
         <v>30</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G18" s="2">
-        <v>1</v>
-      </c>
-      <c r="H18" s="2">
+        <v>121</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I18" s="2">
+        <v>1</v>
+      </c>
+      <c r="J18" s="2">
         <v>2</v>
       </c>
     </row>
@@ -4924,7 +5164,7 @@
         <v>61</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>20</v>
@@ -4933,12 +5173,18 @@
         <v>30</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G19" s="2">
-        <v>3</v>
-      </c>
-      <c r="H19" s="2">
+        <v>124</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I19" s="2">
+        <v>3</v>
+      </c>
+      <c r="J19" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4950,7 +5196,7 @@
         <v>61</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>16</v>
@@ -4959,12 +5205,18 @@
         <v>22</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G20" s="2">
-        <v>2</v>
-      </c>
-      <c r="H20" s="2">
+        <v>109</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I20" s="2">
+        <v>2</v>
+      </c>
+      <c r="J20" s="2">
         <v>2</v>
       </c>
     </row>
@@ -4976,7 +5228,7 @@
         <v>61</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>16</v>
@@ -4985,12 +5237,18 @@
         <v>24</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G21" s="2">
-        <v>0</v>
-      </c>
-      <c r="H21" s="2">
+        <v>112</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
         <v>3</v>
       </c>
     </row>
@@ -5002,7 +5260,7 @@
         <v>61</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>16</v>
@@ -5011,12 +5269,18 @@
         <v>28</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G22" s="2">
-        <v>2</v>
-      </c>
-      <c r="H22" s="2">
+        <v>115</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I22" s="2">
+        <v>2</v>
+      </c>
+      <c r="J22" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5028,7 +5292,7 @@
         <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>22</v>
@@ -5037,12 +5301,18 @@
         <v>24</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G23" s="2">
-        <v>3</v>
-      </c>
-      <c r="H23" s="2">
+        <v>118</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I23" s="2">
+        <v>3</v>
+      </c>
+      <c r="J23" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5054,7 +5324,7 @@
         <v>61</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>22</v>
@@ -5063,12 +5333,18 @@
         <v>28</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G24" s="2">
-        <v>1</v>
-      </c>
-      <c r="H24" s="2">
+        <v>121</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I24" s="2">
+        <v>1</v>
+      </c>
+      <c r="J24" s="2">
         <v>2</v>
       </c>
     </row>
@@ -5080,7 +5356,7 @@
         <v>61</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>24</v>
@@ -5089,12 +5365,18 @@
         <v>28</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G25" s="2">
-        <v>3</v>
-      </c>
-      <c r="H25" s="2">
+        <v>124</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I25" s="2">
+        <v>3</v>
+      </c>
+      <c r="J25" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5106,7 +5388,7 @@
         <v>64</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>2</v>
@@ -5115,12 +5397,18 @@
         <v>28</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G26" s="2">
-        <v>1</v>
-      </c>
-      <c r="H26" s="2">
+        <v>131</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I26" s="2">
+        <v>1</v>
+      </c>
+      <c r="J26" s="2">
         <v>2</v>
       </c>
     </row>
@@ -5132,7 +5420,7 @@
         <v>64</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>10</v>
@@ -5141,12 +5429,18 @@
         <v>24</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="G27" s="2">
-        <v>2</v>
-      </c>
-      <c r="H27" s="2">
+        <v>134</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I27" s="2">
+        <v>2</v>
+      </c>
+      <c r="J27" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5158,7 +5452,7 @@
         <v>64</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>12</v>
@@ -5167,12 +5461,18 @@
         <v>22</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G28" s="2">
-        <v>0</v>
-      </c>
-      <c r="H28" s="2">
+        <v>137</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5184,7 +5484,7 @@
         <v>64</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>32</v>
@@ -5193,12 +5493,18 @@
         <v>16</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G29" s="2">
-        <v>1</v>
-      </c>
-      <c r="H29" s="2">
+        <v>140</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I29" s="2">
+        <v>1</v>
+      </c>
+      <c r="J29" s="2">
         <v>2</v>
       </c>
     </row>
@@ -5210,7 +5516,7 @@
         <v>64</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>4</v>
@@ -5219,12 +5525,18 @@
         <v>30</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G30" s="2">
-        <v>2</v>
-      </c>
-      <c r="H30" s="2">
+        <v>143</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I30" s="2">
+        <v>2</v>
+      </c>
+      <c r="J30" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5236,7 +5548,7 @@
         <v>64</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>14</v>
@@ -5245,12 +5557,18 @@
         <v>20</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="G31" s="2">
-        <v>0</v>
-      </c>
-      <c r="H31" s="2">
+        <v>146</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5262,7 +5580,7 @@
         <v>64</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>8</v>
@@ -5271,12 +5589,18 @@
         <v>18</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G32" s="2">
-        <v>1</v>
-      </c>
-      <c r="H32" s="2">
+        <v>149</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I32" s="2">
+        <v>1</v>
+      </c>
+      <c r="J32" s="2">
         <v>2</v>
       </c>
     </row>
@@ -5288,7 +5612,7 @@
         <v>64</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>26</v>
@@ -5297,12 +5621,18 @@
         <v>6</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="G33" s="2">
-        <v>2</v>
-      </c>
-      <c r="H33" s="2">
+        <v>152</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="I33" s="2">
+        <v>2</v>
+      </c>
+      <c r="J33" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5314,7 +5644,7 @@
         <v>67</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>2</v>
@@ -5323,12 +5653,18 @@
         <v>26</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="G34" s="2">
-        <v>2</v>
-      </c>
-      <c r="H34" s="2">
+        <v>155</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I34" s="2">
+        <v>2</v>
+      </c>
+      <c r="J34" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5340,7 +5676,7 @@
         <v>67</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>10</v>
@@ -5349,12 +5685,18 @@
         <v>8</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="G35" s="2">
-        <v>0</v>
-      </c>
-      <c r="H35" s="2">
+        <v>158</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="I35" s="2">
+        <v>0</v>
+      </c>
+      <c r="J35" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5366,7 +5708,7 @@
         <v>67</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>12</v>
@@ -5375,12 +5717,18 @@
         <v>14</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="G36" s="2">
-        <v>1</v>
-      </c>
-      <c r="H36" s="2">
+        <v>161</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I36" s="2">
+        <v>1</v>
+      </c>
+      <c r="J36" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5392,7 +5740,7 @@
         <v>67</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>32</v>
@@ -5401,12 +5749,18 @@
         <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G37" s="2">
-        <v>2</v>
-      </c>
-      <c r="H37" s="2">
+        <v>164</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="I37" s="2">
+        <v>2</v>
+      </c>
+      <c r="J37" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5418,7 +5772,7 @@
         <v>69</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>2</v>
@@ -5427,12 +5781,18 @@
         <v>32</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G38" s="2">
-        <v>1</v>
-      </c>
-      <c r="H38" s="2">
+        <v>167</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I38" s="2">
+        <v>1</v>
+      </c>
+      <c r="J38" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5444,7 +5804,7 @@
         <v>69</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>10</v>
@@ -5453,12 +5813,18 @@
         <v>12</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G39" s="2">
-        <v>0</v>
-      </c>
-      <c r="H39" s="2">
+        <v>170</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I39" s="2">
+        <v>0</v>
+      </c>
+      <c r="J39" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5470,7 +5836,7 @@
         <v>71</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>6</v>
@@ -5479,12 +5845,18 @@
         <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G40" s="2">
-        <v>2</v>
-      </c>
-      <c r="H40" s="2">
+        <v>173</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="I40" s="2">
+        <v>2</v>
+      </c>
+      <c r="J40" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5496,7 +5868,7 @@
         <v>73</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>2</v>
@@ -5505,12 +5877,18 @@
         <v>10</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G41" s="2">
-        <v>2</v>
-      </c>
-      <c r="H41" s="2">
+        <v>176</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I41" s="2">
+        <v>2</v>
+      </c>
+      <c r="J41" s="2">
         <v>2</v>
       </c>
     </row>
@@ -5522,7 +5900,7 @@
         <v>73</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>2</v>
@@ -5531,12 +5909,18 @@
         <v>12</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G42" s="2">
-        <v>0</v>
-      </c>
-      <c r="H42" s="2">
+        <v>177</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I42" s="2">
+        <v>0</v>
+      </c>
+      <c r="J42" s="2">
         <v>3</v>
       </c>
     </row>
@@ -5548,7 +5932,7 @@
         <v>73</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>2</v>
@@ -5557,12 +5941,18 @@
         <v>32</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G43" s="2">
-        <v>2</v>
-      </c>
-      <c r="H43" s="2">
+        <v>178</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I43" s="2">
+        <v>2</v>
+      </c>
+      <c r="J43" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5574,7 +5964,7 @@
         <v>73</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>10</v>
@@ -5583,12 +5973,18 @@
         <v>12</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G44" s="2">
-        <v>3</v>
-      </c>
-      <c r="H44" s="2">
+        <v>179</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I44" s="2">
+        <v>3</v>
+      </c>
+      <c r="J44" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5600,7 +5996,7 @@
         <v>73</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>10</v>
@@ -5609,12 +6005,18 @@
         <v>32</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G45" s="2">
-        <v>1</v>
-      </c>
-      <c r="H45" s="2">
+        <v>180</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I45" s="2">
+        <v>1</v>
+      </c>
+      <c r="J45" s="2">
         <v>2</v>
       </c>
     </row>
@@ -5626,7 +6028,7 @@
         <v>73</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>12</v>
@@ -5635,12 +6037,18 @@
         <v>32</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G46" s="2">
-        <v>3</v>
-      </c>
-      <c r="H46" s="2">
+        <v>181</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I46" s="2">
+        <v>3</v>
+      </c>
+      <c r="J46" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5652,7 +6060,7 @@
         <v>73</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>4</v>
@@ -5661,12 +6069,18 @@
         <v>14</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G47" s="2">
-        <v>2</v>
-      </c>
-      <c r="H47" s="2">
+        <v>176</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I47" s="2">
+        <v>2</v>
+      </c>
+      <c r="J47" s="2">
         <v>2</v>
       </c>
     </row>
@@ -5678,7 +6092,7 @@
         <v>73</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>4</v>
@@ -5687,12 +6101,18 @@
         <v>8</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G48" s="2">
-        <v>0</v>
-      </c>
-      <c r="H48" s="2">
+        <v>177</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I48" s="2">
+        <v>0</v>
+      </c>
+      <c r="J48" s="2">
         <v>3</v>
       </c>
     </row>
@@ -5704,7 +6124,7 @@
         <v>73</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>4</v>
@@ -5713,12 +6133,18 @@
         <v>26</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G49" s="2">
-        <v>2</v>
-      </c>
-      <c r="H49" s="2">
+        <v>178</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I49" s="2">
+        <v>2</v>
+      </c>
+      <c r="J49" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5730,7 +6156,7 @@
         <v>73</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>14</v>
@@ -5739,12 +6165,18 @@
         <v>8</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G50" s="2">
-        <v>3</v>
-      </c>
-      <c r="H50" s="2">
+        <v>179</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I50" s="2">
+        <v>3</v>
+      </c>
+      <c r="J50" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5756,7 +6188,7 @@
         <v>73</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>14</v>
@@ -5765,12 +6197,18 @@
         <v>26</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G51" s="2">
-        <v>1</v>
-      </c>
-      <c r="H51" s="2">
+        <v>180</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I51" s="2">
+        <v>1</v>
+      </c>
+      <c r="J51" s="2">
         <v>2</v>
       </c>
     </row>
@@ -5782,7 +6220,7 @@
         <v>73</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>8</v>
@@ -5791,12 +6229,18 @@
         <v>26</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G52" s="2">
-        <v>3</v>
-      </c>
-      <c r="H52" s="2">
+        <v>181</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I52" s="2">
+        <v>3</v>
+      </c>
+      <c r="J52" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5808,7 +6252,7 @@
         <v>73</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>6</v>
@@ -5817,12 +6261,18 @@
         <v>18</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G53" s="2">
-        <v>2</v>
-      </c>
-      <c r="H53" s="2">
+        <v>176</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I53" s="2">
+        <v>2</v>
+      </c>
+      <c r="J53" s="2">
         <v>2</v>
       </c>
     </row>
@@ -5834,7 +6284,7 @@
         <v>73</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>6</v>
@@ -5843,12 +6293,18 @@
         <v>20</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G54" s="2">
-        <v>0</v>
-      </c>
-      <c r="H54" s="2">
+        <v>177</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I54" s="2">
+        <v>0</v>
+      </c>
+      <c r="J54" s="2">
         <v>3</v>
       </c>
     </row>
@@ -5860,7 +6316,7 @@
         <v>73</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>6</v>
@@ -5869,12 +6325,18 @@
         <v>30</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G55" s="2">
-        <v>2</v>
-      </c>
-      <c r="H55" s="2">
+        <v>178</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I55" s="2">
+        <v>2</v>
+      </c>
+      <c r="J55" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5886,7 +6348,7 @@
         <v>73</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>18</v>
@@ -5895,12 +6357,18 @@
         <v>20</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G56" s="2">
-        <v>3</v>
-      </c>
-      <c r="H56" s="2">
+        <v>179</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I56" s="2">
+        <v>3</v>
+      </c>
+      <c r="J56" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5912,7 +6380,7 @@
         <v>73</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>18</v>
@@ -5921,12 +6389,18 @@
         <v>30</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G57" s="2">
-        <v>1</v>
-      </c>
-      <c r="H57" s="2">
+        <v>180</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I57" s="2">
+        <v>1</v>
+      </c>
+      <c r="J57" s="2">
         <v>2</v>
       </c>
     </row>
@@ -5938,7 +6412,7 @@
         <v>73</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>20</v>
@@ -5947,12 +6421,18 @@
         <v>30</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G58" s="2">
-        <v>3</v>
-      </c>
-      <c r="H58" s="2">
+        <v>181</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I58" s="2">
+        <v>3</v>
+      </c>
+      <c r="J58" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5964,7 +6444,7 @@
         <v>73</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>16</v>
@@ -5973,12 +6453,18 @@
         <v>22</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G59" s="2">
-        <v>2</v>
-      </c>
-      <c r="H59" s="2">
+        <v>176</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I59" s="2">
+        <v>2</v>
+      </c>
+      <c r="J59" s="2">
         <v>2</v>
       </c>
     </row>
@@ -5990,7 +6476,7 @@
         <v>73</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>16</v>
@@ -5999,12 +6485,18 @@
         <v>24</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G60" s="2">
-        <v>0</v>
-      </c>
-      <c r="H60" s="2">
+        <v>177</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I60" s="2">
+        <v>0</v>
+      </c>
+      <c r="J60" s="2">
         <v>3</v>
       </c>
     </row>
@@ -6016,7 +6508,7 @@
         <v>73</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>16</v>
@@ -6025,12 +6517,18 @@
         <v>28</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G61" s="2">
-        <v>2</v>
-      </c>
-      <c r="H61" s="2">
+        <v>178</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I61" s="2">
+        <v>2</v>
+      </c>
+      <c r="J61" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6042,7 +6540,7 @@
         <v>73</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>22</v>
@@ -6051,12 +6549,18 @@
         <v>24</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G62" s="2">
-        <v>3</v>
-      </c>
-      <c r="H62" s="2">
+        <v>179</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I62" s="2">
+        <v>3</v>
+      </c>
+      <c r="J62" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6068,7 +6572,7 @@
         <v>73</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>22</v>
@@ -6077,12 +6581,18 @@
         <v>28</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G63" s="2">
-        <v>1</v>
-      </c>
-      <c r="H63" s="2">
+        <v>180</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I63" s="2">
+        <v>1</v>
+      </c>
+      <c r="J63" s="2">
         <v>2</v>
       </c>
     </row>
@@ -6094,7 +6604,7 @@
         <v>73</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>24</v>
@@ -6103,12 +6613,18 @@
         <v>28</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G64" s="2">
-        <v>3</v>
-      </c>
-      <c r="H64" s="2">
+        <v>181</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I64" s="2">
+        <v>3</v>
+      </c>
+      <c r="J64" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6120,7 +6636,7 @@
         <v>74</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>2</v>
@@ -6129,12 +6645,18 @@
         <v>28</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="G65" s="2">
-        <v>1</v>
-      </c>
-      <c r="H65" s="2">
+        <v>182</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I65" s="2">
+        <v>1</v>
+      </c>
+      <c r="J65" s="2">
         <v>2</v>
       </c>
     </row>
@@ -6146,7 +6668,7 @@
         <v>74</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>10</v>
@@ -6155,12 +6677,18 @@
         <v>24</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="G66" s="2">
-        <v>2</v>
-      </c>
-      <c r="H66" s="2">
+        <v>183</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I66" s="2">
+        <v>2</v>
+      </c>
+      <c r="J66" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6172,7 +6700,7 @@
         <v>74</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>12</v>
@@ -6181,12 +6709,18 @@
         <v>22</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="G67" s="2">
-        <v>0</v>
-      </c>
-      <c r="H67" s="2">
+        <v>184</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I67" s="2">
+        <v>0</v>
+      </c>
+      <c r="J67" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6198,7 +6732,7 @@
         <v>74</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>32</v>
@@ -6207,12 +6741,18 @@
         <v>16</v>
       </c>
       <c r="F68" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G68" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="G68" s="2">
-        <v>1</v>
-      </c>
-      <c r="H68" s="2">
+      <c r="H68" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I68" s="2">
+        <v>1</v>
+      </c>
+      <c r="J68" s="2">
         <v>2</v>
       </c>
     </row>
@@ -6224,7 +6764,7 @@
         <v>74</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>4</v>
@@ -6233,12 +6773,18 @@
         <v>30</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="G69" s="2">
-        <v>2</v>
-      </c>
-      <c r="H69" s="2">
+        <v>186</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I69" s="2">
+        <v>2</v>
+      </c>
+      <c r="J69" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6250,7 +6796,7 @@
         <v>74</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>14</v>
@@ -6259,12 +6805,18 @@
         <v>20</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="G70" s="2">
-        <v>0</v>
-      </c>
-      <c r="H70" s="2">
+        <v>187</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I70" s="2">
+        <v>0</v>
+      </c>
+      <c r="J70" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6276,7 +6828,7 @@
         <v>74</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>8</v>
@@ -6285,12 +6837,18 @@
         <v>18</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="G71" s="2">
-        <v>1</v>
-      </c>
-      <c r="H71" s="2">
+        <v>188</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I71" s="2">
+        <v>1</v>
+      </c>
+      <c r="J71" s="2">
         <v>2</v>
       </c>
     </row>
@@ -6302,7 +6860,7 @@
         <v>74</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>26</v>
@@ -6311,12 +6869,18 @@
         <v>6</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="G72" s="2">
-        <v>2</v>
-      </c>
-      <c r="H72" s="2">
+        <v>189</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="I72" s="2">
+        <v>2</v>
+      </c>
+      <c r="J72" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6328,7 +6892,7 @@
         <v>75</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>2</v>
@@ -6337,12 +6901,18 @@
         <v>26</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="G73" s="2">
-        <v>2</v>
-      </c>
-      <c r="H73" s="2">
+        <v>190</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I73" s="2">
+        <v>2</v>
+      </c>
+      <c r="J73" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6354,7 +6924,7 @@
         <v>75</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>10</v>
@@ -6363,12 +6933,18 @@
         <v>8</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="G74" s="2">
-        <v>0</v>
-      </c>
-      <c r="H74" s="2">
+        <v>191</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="I74" s="2">
+        <v>0</v>
+      </c>
+      <c r="J74" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6380,7 +6956,7 @@
         <v>75</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>12</v>
@@ -6389,12 +6965,18 @@
         <v>14</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="G75" s="2">
-        <v>1</v>
-      </c>
-      <c r="H75" s="2">
+        <v>192</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I75" s="2">
+        <v>1</v>
+      </c>
+      <c r="J75" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6406,7 +6988,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>32</v>
@@ -6415,12 +6997,18 @@
         <v>4</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="G76" s="2">
-        <v>2</v>
-      </c>
-      <c r="H76" s="2">
+        <v>193</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="I76" s="2">
+        <v>2</v>
+      </c>
+      <c r="J76" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6432,7 +7020,7 @@
         <v>76</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>2</v>
@@ -6441,12 +7029,18 @@
         <v>32</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="G77" s="2">
-        <v>1</v>
-      </c>
-      <c r="H77" s="2">
+        <v>194</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I77" s="2">
+        <v>1</v>
+      </c>
+      <c r="J77" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6458,7 +7052,7 @@
         <v>76</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>10</v>
@@ -6467,12 +7061,18 @@
         <v>12</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="G78" s="2">
-        <v>0</v>
-      </c>
-      <c r="H78" s="2">
+        <v>195</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I78" s="2">
+        <v>0</v>
+      </c>
+      <c r="J78" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6484,7 +7084,7 @@
         <v>77</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>8</v>
@@ -6493,12 +7093,18 @@
         <v>4</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G79" s="2">
-        <v>2</v>
-      </c>
-      <c r="H79" s="2">
+        <v>196</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="I79" s="2">
+        <v>2</v>
+      </c>
+      <c r="J79" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6510,7 +7116,7 @@
         <v>78</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>2</v>
@@ -6519,12 +7125,18 @@
         <v>10</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G80" s="2">
-        <v>2</v>
-      </c>
-      <c r="H80" s="2">
+        <v>197</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I80" s="2">
+        <v>2</v>
+      </c>
+      <c r="J80" s="2">
         <v>2</v>
       </c>
     </row>
@@ -6536,7 +7148,7 @@
         <v>78</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>2</v>
@@ -6545,12 +7157,18 @@
         <v>12</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="G81" s="2">
-        <v>0</v>
-      </c>
-      <c r="H81" s="2">
+        <v>198</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I81" s="2">
+        <v>0</v>
+      </c>
+      <c r="J81" s="2">
         <v>3</v>
       </c>
     </row>
@@ -6562,7 +7180,7 @@
         <v>78</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>2</v>
@@ -6571,12 +7189,18 @@
         <v>32</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="G82" s="2">
-        <v>2</v>
-      </c>
-      <c r="H82" s="2">
+        <v>199</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I82" s="2">
+        <v>2</v>
+      </c>
+      <c r="J82" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6588,7 +7212,7 @@
         <v>78</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>10</v>
@@ -6597,12 +7221,18 @@
         <v>12</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="G83" s="2">
-        <v>3</v>
-      </c>
-      <c r="H83" s="2">
+        <v>200</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I83" s="2">
+        <v>3</v>
+      </c>
+      <c r="J83" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6614,7 +7244,7 @@
         <v>78</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>10</v>
@@ -6623,12 +7253,18 @@
         <v>32</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="G84" s="2">
-        <v>1</v>
-      </c>
-      <c r="H84" s="2">
+        <v>201</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I84" s="2">
+        <v>1</v>
+      </c>
+      <c r="J84" s="2">
         <v>2</v>
       </c>
     </row>
@@ -6640,7 +7276,7 @@
         <v>78</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>12</v>
@@ -6649,12 +7285,18 @@
         <v>32</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="G85" s="2">
-        <v>3</v>
-      </c>
-      <c r="H85" s="2">
+        <v>202</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I85" s="2">
+        <v>3</v>
+      </c>
+      <c r="J85" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6666,7 +7308,7 @@
         <v>78</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>4</v>
@@ -6675,12 +7317,18 @@
         <v>14</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G86" s="2">
-        <v>2</v>
-      </c>
-      <c r="H86" s="2">
+        <v>197</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I86" s="2">
+        <v>2</v>
+      </c>
+      <c r="J86" s="2">
         <v>2</v>
       </c>
     </row>
@@ -6692,7 +7340,7 @@
         <v>78</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>4</v>
@@ -6701,12 +7349,18 @@
         <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="G87" s="2">
-        <v>0</v>
-      </c>
-      <c r="H87" s="2">
+        <v>198</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I87" s="2">
+        <v>0</v>
+      </c>
+      <c r="J87" s="2">
         <v>3</v>
       </c>
     </row>
@@ -6718,7 +7372,7 @@
         <v>78</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>4</v>
@@ -6727,12 +7381,18 @@
         <v>26</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="G88" s="2">
-        <v>2</v>
-      </c>
-      <c r="H88" s="2">
+        <v>199</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I88" s="2">
+        <v>2</v>
+      </c>
+      <c r="J88" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6744,7 +7404,7 @@
         <v>78</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>14</v>
@@ -6753,12 +7413,18 @@
         <v>8</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="G89" s="2">
-        <v>3</v>
-      </c>
-      <c r="H89" s="2">
+        <v>200</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I89" s="2">
+        <v>3</v>
+      </c>
+      <c r="J89" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6770,7 +7436,7 @@
         <v>78</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>14</v>
@@ -6779,12 +7445,18 @@
         <v>26</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="G90" s="2">
-        <v>1</v>
-      </c>
-      <c r="H90" s="2">
+        <v>201</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I90" s="2">
+        <v>1</v>
+      </c>
+      <c r="J90" s="2">
         <v>2</v>
       </c>
     </row>
@@ -6796,7 +7468,7 @@
         <v>78</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>8</v>
@@ -6805,12 +7477,18 @@
         <v>26</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="G91" s="2">
-        <v>3</v>
-      </c>
-      <c r="H91" s="2">
+        <v>202</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I91" s="2">
+        <v>3</v>
+      </c>
+      <c r="J91" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6822,7 +7500,7 @@
         <v>78</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>6</v>
@@ -6831,12 +7509,18 @@
         <v>18</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G92" s="2">
-        <v>2</v>
-      </c>
-      <c r="H92" s="2">
+        <v>197</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I92" s="2">
+        <v>2</v>
+      </c>
+      <c r="J92" s="2">
         <v>2</v>
       </c>
     </row>
@@ -6848,7 +7532,7 @@
         <v>78</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>6</v>
@@ -6857,12 +7541,18 @@
         <v>20</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="G93" s="2">
-        <v>0</v>
-      </c>
-      <c r="H93" s="2">
+        <v>198</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I93" s="2">
+        <v>0</v>
+      </c>
+      <c r="J93" s="2">
         <v>3</v>
       </c>
     </row>
@@ -6874,7 +7564,7 @@
         <v>78</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>6</v>
@@ -6883,12 +7573,18 @@
         <v>30</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="G94" s="2">
-        <v>2</v>
-      </c>
-      <c r="H94" s="2">
+        <v>199</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I94" s="2">
+        <v>2</v>
+      </c>
+      <c r="J94" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6900,7 +7596,7 @@
         <v>78</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>18</v>
@@ -6909,12 +7605,18 @@
         <v>20</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="G95" s="2">
-        <v>3</v>
-      </c>
-      <c r="H95" s="2">
+        <v>200</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I95" s="2">
+        <v>3</v>
+      </c>
+      <c r="J95" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6926,7 +7628,7 @@
         <v>78</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>18</v>
@@ -6935,12 +7637,18 @@
         <v>30</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="G96" s="2">
-        <v>1</v>
-      </c>
-      <c r="H96" s="2">
+        <v>201</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I96" s="2">
+        <v>1</v>
+      </c>
+      <c r="J96" s="2">
         <v>2</v>
       </c>
     </row>
@@ -6952,7 +7660,7 @@
         <v>78</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>20</v>
@@ -6961,12 +7669,18 @@
         <v>30</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="G97" s="2">
-        <v>3</v>
-      </c>
-      <c r="H97" s="2">
+        <v>202</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I97" s="2">
+        <v>3</v>
+      </c>
+      <c r="J97" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6978,7 +7692,7 @@
         <v>78</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>16</v>
@@ -6987,12 +7701,18 @@
         <v>22</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G98" s="2">
-        <v>2</v>
-      </c>
-      <c r="H98" s="2">
+        <v>197</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I98" s="2">
+        <v>2</v>
+      </c>
+      <c r="J98" s="2">
         <v>2</v>
       </c>
     </row>
@@ -7004,7 +7724,7 @@
         <v>78</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>16</v>
@@ -7013,12 +7733,18 @@
         <v>24</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="G99" s="2">
-        <v>0</v>
-      </c>
-      <c r="H99" s="2">
+        <v>198</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I99" s="2">
+        <v>0</v>
+      </c>
+      <c r="J99" s="2">
         <v>3</v>
       </c>
     </row>
@@ -7030,7 +7756,7 @@
         <v>78</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>16</v>
@@ -7039,12 +7765,18 @@
         <v>28</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="G100" s="2">
-        <v>2</v>
-      </c>
-      <c r="H100" s="2">
+        <v>199</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I100" s="2">
+        <v>2</v>
+      </c>
+      <c r="J100" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7056,7 +7788,7 @@
         <v>78</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>22</v>
@@ -7065,12 +7797,18 @@
         <v>24</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="G101" s="2">
-        <v>3</v>
-      </c>
-      <c r="H101" s="2">
+        <v>200</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I101" s="2">
+        <v>3</v>
+      </c>
+      <c r="J101" s="2">
         <v>1</v>
       </c>
     </row>
@@ -7082,7 +7820,7 @@
         <v>78</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>22</v>
@@ -7091,12 +7829,18 @@
         <v>28</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="G102" s="2">
-        <v>1</v>
-      </c>
-      <c r="H102" s="2">
+        <v>201</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I102" s="2">
+        <v>1</v>
+      </c>
+      <c r="J102" s="2">
         <v>2</v>
       </c>
     </row>
@@ -7108,7 +7852,7 @@
         <v>78</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>24</v>
@@ -7117,12 +7861,18 @@
         <v>28</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="G103" s="2">
-        <v>3</v>
-      </c>
-      <c r="H103" s="2">
+        <v>202</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I103" s="2">
+        <v>3</v>
+      </c>
+      <c r="J103" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7134,7 +7884,7 @@
         <v>79</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>2</v>
@@ -7143,12 +7893,18 @@
         <v>28</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G104" s="2">
-        <v>1</v>
-      </c>
-      <c r="H104" s="2">
+        <v>203</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I104" s="2">
+        <v>1</v>
+      </c>
+      <c r="J104" s="2">
         <v>2</v>
       </c>
     </row>
@@ -7160,7 +7916,7 @@
         <v>79</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>10</v>
@@ -7169,12 +7925,18 @@
         <v>24</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="G105" s="2">
-        <v>2</v>
-      </c>
-      <c r="H105" s="2">
+        <v>204</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I105" s="2">
+        <v>2</v>
+      </c>
+      <c r="J105" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7186,7 +7948,7 @@
         <v>79</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>12</v>
@@ -7195,12 +7957,18 @@
         <v>22</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="G106" s="2">
-        <v>0</v>
-      </c>
-      <c r="H106" s="2">
+        <v>205</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I106" s="2">
+        <v>0</v>
+      </c>
+      <c r="J106" s="2">
         <v>1</v>
       </c>
     </row>
@@ -7212,7 +7980,7 @@
         <v>79</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>32</v>
@@ -7221,12 +7989,18 @@
         <v>16</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="G107" s="2">
-        <v>1</v>
-      </c>
-      <c r="H107" s="2">
+        <v>206</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I107" s="2">
+        <v>1</v>
+      </c>
+      <c r="J107" s="2">
         <v>2</v>
       </c>
     </row>
@@ -7238,7 +8012,7 @@
         <v>79</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>4</v>
@@ -7247,12 +8021,18 @@
         <v>30</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G108" s="2">
-        <v>2</v>
-      </c>
-      <c r="H108" s="2">
+        <v>207</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I108" s="2">
+        <v>2</v>
+      </c>
+      <c r="J108" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7264,7 +8044,7 @@
         <v>79</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>14</v>
@@ -7273,12 +8053,18 @@
         <v>20</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="G109" s="2">
-        <v>0</v>
-      </c>
-      <c r="H109" s="2">
+        <v>208</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I109" s="2">
+        <v>0</v>
+      </c>
+      <c r="J109" s="2">
         <v>1</v>
       </c>
     </row>
@@ -7290,7 +8076,7 @@
         <v>79</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>8</v>
@@ -7299,12 +8085,18 @@
         <v>18</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="G110" s="2">
-        <v>1</v>
-      </c>
-      <c r="H110" s="2">
+        <v>209</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I110" s="2">
+        <v>1</v>
+      </c>
+      <c r="J110" s="2">
         <v>2</v>
       </c>
     </row>
@@ -7316,7 +8108,7 @@
         <v>79</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>26</v>
@@ -7325,12 +8117,18 @@
         <v>6</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="G111" s="2">
-        <v>2</v>
-      </c>
-      <c r="H111" s="2">
+        <v>210</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="I111" s="2">
+        <v>2</v>
+      </c>
+      <c r="J111" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7342,7 +8140,7 @@
         <v>80</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>2</v>
@@ -7351,12 +8149,18 @@
         <v>26</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="G112" s="2">
-        <v>2</v>
-      </c>
-      <c r="H112" s="2">
+        <v>211</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I112" s="2">
+        <v>2</v>
+      </c>
+      <c r="J112" s="2">
         <v>1</v>
       </c>
     </row>
@@ -7368,7 +8172,7 @@
         <v>80</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>10</v>
@@ -7377,12 +8181,18 @@
         <v>8</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G113" s="2">
-        <v>0</v>
-      </c>
-      <c r="H113" s="2">
+        <v>212</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="I113" s="2">
+        <v>0</v>
+      </c>
+      <c r="J113" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7394,7 +8204,7 @@
         <v>80</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>12</v>
@@ -7403,12 +8213,18 @@
         <v>14</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G114" s="2">
-        <v>1</v>
-      </c>
-      <c r="H114" s="2">
+        <v>213</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I114" s="2">
+        <v>1</v>
+      </c>
+      <c r="J114" s="2">
         <v>1</v>
       </c>
     </row>
@@ -7420,7 +8236,7 @@
         <v>80</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>32</v>
@@ -7429,12 +8245,18 @@
         <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="G115" s="2">
-        <v>2</v>
-      </c>
-      <c r="H115" s="2">
+        <v>214</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="I115" s="2">
+        <v>2</v>
+      </c>
+      <c r="J115" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7446,7 +8268,7 @@
         <v>81</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>2</v>
@@ -7455,12 +8277,18 @@
         <v>32</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="G116" s="2">
-        <v>1</v>
-      </c>
-      <c r="H116" s="2">
+        <v>215</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I116" s="2">
+        <v>1</v>
+      </c>
+      <c r="J116" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7472,7 +8300,7 @@
         <v>81</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>10</v>
@@ -7481,12 +8309,18 @@
         <v>12</v>
       </c>
       <c r="F117" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H117" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="G117" s="2">
-        <v>0</v>
-      </c>
-      <c r="H117" s="2">
+      <c r="I117" s="2">
+        <v>0</v>
+      </c>
+      <c r="J117" s="2">
         <v>1</v>
       </c>
     </row>
@@ -7498,7 +8332,7 @@
         <v>82</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>2</v>
@@ -7507,12 +8341,18 @@
         <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="G118" s="2">
-        <v>2</v>
-      </c>
-      <c r="H118" s="2">
+        <v>217</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="I118" s="2">
+        <v>2</v>
+      </c>
+      <c r="J118" s="2">
         <v>1</v>
       </c>
     </row>
@@ -7524,7 +8364,7 @@
         <v>83</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>2</v>
@@ -7533,12 +8373,18 @@
         <v>10</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="G119" s="2">
-        <v>2</v>
-      </c>
-      <c r="H119" s="2">
+        <v>218</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I119" s="2">
+        <v>2</v>
+      </c>
+      <c r="J119" s="2">
         <v>2</v>
       </c>
     </row>
@@ -7550,7 +8396,7 @@
         <v>83</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>2</v>
@@ -7559,12 +8405,18 @@
         <v>12</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G120" s="2">
-        <v>0</v>
-      </c>
-      <c r="H120" s="2">
+        <v>219</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I120" s="2">
+        <v>0</v>
+      </c>
+      <c r="J120" s="2">
         <v>3</v>
       </c>
     </row>
@@ -7576,7 +8428,7 @@
         <v>83</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>2</v>
@@ -7585,12 +8437,18 @@
         <v>32</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G121" s="2">
-        <v>2</v>
-      </c>
-      <c r="H121" s="2">
+        <v>220</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I121" s="2">
+        <v>2</v>
+      </c>
+      <c r="J121" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7602,7 +8460,7 @@
         <v>83</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>10</v>
@@ -7611,12 +8469,18 @@
         <v>12</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G122" s="2">
-        <v>3</v>
-      </c>
-      <c r="H122" s="2">
+        <v>221</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I122" s="2">
+        <v>3</v>
+      </c>
+      <c r="J122" s="2">
         <v>1</v>
       </c>
     </row>
@@ -7628,7 +8492,7 @@
         <v>83</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>10</v>
@@ -7637,12 +8501,18 @@
         <v>32</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="G123" s="2">
-        <v>1</v>
-      </c>
-      <c r="H123" s="2">
+        <v>222</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I123" s="2">
+        <v>1</v>
+      </c>
+      <c r="J123" s="2">
         <v>2</v>
       </c>
     </row>
@@ -7654,7 +8524,7 @@
         <v>83</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>12</v>
@@ -7663,12 +8533,18 @@
         <v>32</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="G124" s="2">
-        <v>3</v>
-      </c>
-      <c r="H124" s="2">
+        <v>223</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I124" s="2">
+        <v>3</v>
+      </c>
+      <c r="J124" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7680,7 +8556,7 @@
         <v>83</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>4</v>
@@ -7689,12 +8565,18 @@
         <v>14</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="G125" s="2">
-        <v>2</v>
-      </c>
-      <c r="H125" s="2">
+        <v>218</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I125" s="2">
+        <v>2</v>
+      </c>
+      <c r="J125" s="2">
         <v>2</v>
       </c>
     </row>
@@ -7706,7 +8588,7 @@
         <v>83</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>4</v>
@@ -7715,12 +8597,18 @@
         <v>8</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G126" s="2">
-        <v>0</v>
-      </c>
-      <c r="H126" s="2">
+        <v>219</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I126" s="2">
+        <v>0</v>
+      </c>
+      <c r="J126" s="2">
         <v>3</v>
       </c>
     </row>
@@ -7732,7 +8620,7 @@
         <v>83</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>4</v>
@@ -7741,12 +8629,18 @@
         <v>26</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G127" s="2">
-        <v>2</v>
-      </c>
-      <c r="H127" s="2">
+        <v>220</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I127" s="2">
+        <v>2</v>
+      </c>
+      <c r="J127" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7758,7 +8652,7 @@
         <v>83</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>14</v>
@@ -7767,12 +8661,18 @@
         <v>8</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G128" s="2">
-        <v>3</v>
-      </c>
-      <c r="H128" s="2">
+        <v>221</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I128" s="2">
+        <v>3</v>
+      </c>
+      <c r="J128" s="2">
         <v>1</v>
       </c>
     </row>
@@ -7784,7 +8684,7 @@
         <v>83</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>14</v>
@@ -7793,12 +8693,18 @@
         <v>26</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="G129" s="2">
-        <v>1</v>
-      </c>
-      <c r="H129" s="2">
+        <v>222</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I129" s="2">
+        <v>1</v>
+      </c>
+      <c r="J129" s="2">
         <v>2</v>
       </c>
     </row>
@@ -7810,7 +8716,7 @@
         <v>83</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>8</v>
@@ -7819,12 +8725,18 @@
         <v>26</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="G130" s="2">
-        <v>3</v>
-      </c>
-      <c r="H130" s="2">
+        <v>223</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I130" s="2">
+        <v>3</v>
+      </c>
+      <c r="J130" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7836,7 +8748,7 @@
         <v>83</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>6</v>
@@ -7845,12 +8757,18 @@
         <v>18</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="G131" s="2">
-        <v>2</v>
-      </c>
-      <c r="H131" s="2">
+        <v>218</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I131" s="2">
+        <v>2</v>
+      </c>
+      <c r="J131" s="2">
         <v>2</v>
       </c>
     </row>
@@ -7862,7 +8780,7 @@
         <v>83</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>6</v>
@@ -7871,12 +8789,18 @@
         <v>20</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G132" s="2">
-        <v>0</v>
-      </c>
-      <c r="H132" s="2">
+        <v>219</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I132" s="2">
+        <v>0</v>
+      </c>
+      <c r="J132" s="2">
         <v>3</v>
       </c>
     </row>
@@ -7888,7 +8812,7 @@
         <v>83</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>6</v>
@@ -7897,12 +8821,18 @@
         <v>30</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G133" s="2">
-        <v>2</v>
-      </c>
-      <c r="H133" s="2">
+        <v>220</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I133" s="2">
+        <v>2</v>
+      </c>
+      <c r="J133" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7914,7 +8844,7 @@
         <v>83</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>18</v>
@@ -7923,12 +8853,18 @@
         <v>20</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G134" s="2">
-        <v>3</v>
-      </c>
-      <c r="H134" s="2">
+        <v>221</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I134" s="2">
+        <v>3</v>
+      </c>
+      <c r="J134" s="2">
         <v>1</v>
       </c>
     </row>
@@ -7940,7 +8876,7 @@
         <v>83</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>18</v>
@@ -7949,12 +8885,18 @@
         <v>30</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="G135" s="2">
-        <v>1</v>
-      </c>
-      <c r="H135" s="2">
+        <v>222</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I135" s="2">
+        <v>1</v>
+      </c>
+      <c r="J135" s="2">
         <v>2</v>
       </c>
     </row>
@@ -7966,7 +8908,7 @@
         <v>83</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>20</v>
@@ -7975,12 +8917,18 @@
         <v>30</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="G136" s="2">
-        <v>3</v>
-      </c>
-      <c r="H136" s="2">
+        <v>223</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I136" s="2">
+        <v>3</v>
+      </c>
+      <c r="J136" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7992,7 +8940,7 @@
         <v>83</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>16</v>
@@ -8001,12 +8949,18 @@
         <v>22</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="G137" s="2">
-        <v>2</v>
-      </c>
-      <c r="H137" s="2">
+        <v>218</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I137" s="2">
+        <v>2</v>
+      </c>
+      <c r="J137" s="2">
         <v>2</v>
       </c>
     </row>
@@ -8018,7 +8972,7 @@
         <v>83</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>16</v>
@@ -8027,12 +8981,18 @@
         <v>24</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G138" s="2">
-        <v>0</v>
-      </c>
-      <c r="H138" s="2">
+        <v>219</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I138" s="2">
+        <v>0</v>
+      </c>
+      <c r="J138" s="2">
         <v>3</v>
       </c>
     </row>
@@ -8044,7 +9004,7 @@
         <v>83</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>16</v>
@@ -8053,12 +9013,18 @@
         <v>28</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G139" s="2">
-        <v>2</v>
-      </c>
-      <c r="H139" s="2">
+        <v>220</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I139" s="2">
+        <v>2</v>
+      </c>
+      <c r="J139" s="2">
         <v>0</v>
       </c>
     </row>
@@ -8070,7 +9036,7 @@
         <v>83</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>22</v>
@@ -8079,12 +9045,18 @@
         <v>24</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G140" s="2">
-        <v>3</v>
-      </c>
-      <c r="H140" s="2">
+        <v>221</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I140" s="2">
+        <v>3</v>
+      </c>
+      <c r="J140" s="2">
         <v>1</v>
       </c>
     </row>
@@ -8096,7 +9068,7 @@
         <v>83</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>22</v>
@@ -8105,12 +9077,18 @@
         <v>28</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="G141" s="2">
-        <v>1</v>
-      </c>
-      <c r="H141" s="2">
+        <v>222</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H141" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I141" s="2">
+        <v>1</v>
+      </c>
+      <c r="J141" s="2">
         <v>2</v>
       </c>
     </row>
@@ -8122,7 +9100,7 @@
         <v>83</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>24</v>
@@ -8131,12 +9109,18 @@
         <v>28</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="G142" s="2">
-        <v>3</v>
-      </c>
-      <c r="H142" s="2">
+        <v>223</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I142" s="2">
+        <v>3</v>
+      </c>
+      <c r="J142" s="2">
         <v>0</v>
       </c>
     </row>
@@ -8148,7 +9132,7 @@
         <v>84</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>2</v>
@@ -8157,12 +9141,18 @@
         <v>28</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="G143" s="2">
-        <v>1</v>
-      </c>
-      <c r="H143" s="2">
+        <v>224</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H143" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I143" s="2">
+        <v>1</v>
+      </c>
+      <c r="J143" s="2">
         <v>2</v>
       </c>
     </row>
@@ -8174,7 +9164,7 @@
         <v>84</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>10</v>
@@ -8183,12 +9173,18 @@
         <v>24</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="G144" s="2">
-        <v>2</v>
-      </c>
-      <c r="H144" s="2">
+        <v>225</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I144" s="2">
+        <v>2</v>
+      </c>
+      <c r="J144" s="2">
         <v>0</v>
       </c>
     </row>
@@ -8200,7 +9196,7 @@
         <v>84</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>12</v>
@@ -8209,12 +9205,18 @@
         <v>22</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="G145" s="2">
-        <v>0</v>
-      </c>
-      <c r="H145" s="2">
+        <v>226</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I145" s="2">
+        <v>0</v>
+      </c>
+      <c r="J145" s="2">
         <v>1</v>
       </c>
     </row>
@@ -8226,7 +9228,7 @@
         <v>84</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>32</v>
@@ -8235,12 +9237,18 @@
         <v>16</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G146" s="2">
-        <v>1</v>
-      </c>
-      <c r="H146" s="2">
+        <v>227</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H146" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I146" s="2">
+        <v>1</v>
+      </c>
+      <c r="J146" s="2">
         <v>2</v>
       </c>
     </row>
@@ -8252,7 +9260,7 @@
         <v>84</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>4</v>
@@ -8261,12 +9269,18 @@
         <v>30</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="G147" s="2">
-        <v>2</v>
-      </c>
-      <c r="H147" s="2">
+        <v>228</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H147" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I147" s="2">
+        <v>2</v>
+      </c>
+      <c r="J147" s="2">
         <v>0</v>
       </c>
     </row>
@@ -8278,7 +9292,7 @@
         <v>84</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>14</v>
@@ -8287,12 +9301,18 @@
         <v>20</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="G148" s="2">
-        <v>0</v>
-      </c>
-      <c r="H148" s="2">
+        <v>229</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H148" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I148" s="2">
+        <v>0</v>
+      </c>
+      <c r="J148" s="2">
         <v>1</v>
       </c>
     </row>
@@ -8304,7 +9324,7 @@
         <v>84</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>8</v>
@@ -8313,12 +9333,18 @@
         <v>18</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="G149" s="2">
-        <v>1</v>
-      </c>
-      <c r="H149" s="2">
+        <v>230</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I149" s="2">
+        <v>1</v>
+      </c>
+      <c r="J149" s="2">
         <v>2</v>
       </c>
     </row>
@@ -8330,7 +9356,7 @@
         <v>84</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>26</v>
@@ -8339,12 +9365,18 @@
         <v>6</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G150" s="2">
-        <v>2</v>
-      </c>
-      <c r="H150" s="2">
+        <v>231</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H150" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="I150" s="2">
+        <v>2</v>
+      </c>
+      <c r="J150" s="2">
         <v>0</v>
       </c>
     </row>
@@ -8356,7 +9388,7 @@
         <v>85</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>2</v>
@@ -8365,12 +9397,18 @@
         <v>26</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="G151" s="2">
-        <v>2</v>
-      </c>
-      <c r="H151" s="2">
+        <v>232</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H151" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I151" s="2">
+        <v>2</v>
+      </c>
+      <c r="J151" s="2">
         <v>1</v>
       </c>
     </row>
@@ -8382,7 +9420,7 @@
         <v>85</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>10</v>
@@ -8391,12 +9429,18 @@
         <v>8</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="G152" s="2">
-        <v>0</v>
-      </c>
-      <c r="H152" s="2">
+        <v>233</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H152" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="I152" s="2">
+        <v>0</v>
+      </c>
+      <c r="J152" s="2">
         <v>0</v>
       </c>
     </row>
@@ -8408,7 +9452,7 @@
         <v>85</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>12</v>
@@ -8417,12 +9461,18 @@
         <v>14</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="G153" s="2">
-        <v>1</v>
-      </c>
-      <c r="H153" s="2">
+        <v>234</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H153" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I153" s="2">
+        <v>1</v>
+      </c>
+      <c r="J153" s="2">
         <v>1</v>
       </c>
     </row>
@@ -8434,7 +9484,7 @@
         <v>85</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>32</v>
@@ -8443,12 +9493,18 @@
         <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="G154" s="2">
-        <v>2</v>
-      </c>
-      <c r="H154" s="2">
+        <v>235</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="H154" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="I154" s="2">
+        <v>2</v>
+      </c>
+      <c r="J154" s="2">
         <v>0</v>
       </c>
     </row>
@@ -8460,7 +9516,7 @@
         <v>86</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>2</v>
@@ -8469,12 +9525,18 @@
         <v>32</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G155" s="2">
-        <v>1</v>
-      </c>
-      <c r="H155" s="2">
+        <v>236</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H155" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I155" s="2">
+        <v>1</v>
+      </c>
+      <c r="J155" s="2">
         <v>0</v>
       </c>
     </row>
@@ -8486,7 +9548,7 @@
         <v>86</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>10</v>
@@ -8495,12 +9557,18 @@
         <v>12</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G156" s="2">
-        <v>0</v>
-      </c>
-      <c r="H156" s="2">
+        <v>237</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H156" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I156" s="2">
+        <v>0</v>
+      </c>
+      <c r="J156" s="2">
         <v>1</v>
       </c>
     </row>
@@ -8512,7 +9580,7 @@
         <v>87</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>4</v>
@@ -8521,12 +9589,18 @@
         <v>2</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="G157" s="2">
-        <v>2</v>
-      </c>
-      <c r="H157" s="2">
+        <v>238</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H157" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="I157" s="2">
+        <v>2</v>
+      </c>
+      <c r="J157" s="2">
         <v>1</v>
       </c>
     </row>
@@ -8538,7 +9612,7 @@
         <v>88</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>2</v>
@@ -8547,12 +9621,18 @@
         <v>10</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="G158" s="2">
-        <v>2</v>
-      </c>
-      <c r="H158" s="2">
+        <v>239</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H158" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I158" s="2">
+        <v>2</v>
+      </c>
+      <c r="J158" s="2">
         <v>2</v>
       </c>
     </row>
@@ -8564,7 +9644,7 @@
         <v>88</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>2</v>
@@ -8573,12 +9653,18 @@
         <v>12</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="G159" s="2">
-        <v>0</v>
-      </c>
-      <c r="H159" s="2">
+        <v>240</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H159" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I159" s="2">
+        <v>0</v>
+      </c>
+      <c r="J159" s="2">
         <v>3</v>
       </c>
     </row>
@@ -8590,7 +9676,7 @@
         <v>88</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>2</v>
@@ -8599,12 +9685,18 @@
         <v>32</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="G160" s="2">
-        <v>2</v>
-      </c>
-      <c r="H160" s="2">
+        <v>241</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H160" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I160" s="2">
+        <v>2</v>
+      </c>
+      <c r="J160" s="2">
         <v>0</v>
       </c>
     </row>
@@ -8616,7 +9708,7 @@
         <v>88</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>10</v>
@@ -8625,12 +9717,18 @@
         <v>12</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G161" s="2">
-        <v>3</v>
-      </c>
-      <c r="H161" s="2">
+        <v>242</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H161" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I161" s="2">
+        <v>3</v>
+      </c>
+      <c r="J161" s="2">
         <v>1</v>
       </c>
     </row>
@@ -8642,7 +9740,7 @@
         <v>88</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>10</v>
@@ -8651,12 +9749,18 @@
         <v>32</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G162" s="2">
-        <v>1</v>
-      </c>
-      <c r="H162" s="2">
+        <v>243</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H162" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I162" s="2">
+        <v>1</v>
+      </c>
+      <c r="J162" s="2">
         <v>2</v>
       </c>
     </row>
@@ -8668,7 +9772,7 @@
         <v>88</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>12</v>
@@ -8677,12 +9781,18 @@
         <v>32</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="G163" s="2">
-        <v>3</v>
-      </c>
-      <c r="H163" s="2">
+        <v>244</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H163" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I163" s="2">
+        <v>3</v>
+      </c>
+      <c r="J163" s="2">
         <v>0</v>
       </c>
     </row>
@@ -8694,7 +9804,7 @@
         <v>88</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D164" s="1" t="s">
         <v>4</v>
@@ -8703,12 +9813,18 @@
         <v>14</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="G164" s="2">
-        <v>2</v>
-      </c>
-      <c r="H164" s="2">
+        <v>239</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H164" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I164" s="2">
+        <v>2</v>
+      </c>
+      <c r="J164" s="2">
         <v>2</v>
       </c>
     </row>
@@ -8720,7 +9836,7 @@
         <v>88</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>4</v>
@@ -8729,12 +9845,18 @@
         <v>8</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="G165" s="2">
-        <v>0</v>
-      </c>
-      <c r="H165" s="2">
+        <v>240</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H165" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I165" s="2">
+        <v>0</v>
+      </c>
+      <c r="J165" s="2">
         <v>3</v>
       </c>
     </row>
@@ -8746,7 +9868,7 @@
         <v>88</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>4</v>
@@ -8755,12 +9877,18 @@
         <v>26</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="G166" s="2">
-        <v>2</v>
-      </c>
-      <c r="H166" s="2">
+        <v>241</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H166" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I166" s="2">
+        <v>2</v>
+      </c>
+      <c r="J166" s="2">
         <v>0</v>
       </c>
     </row>
@@ -8772,7 +9900,7 @@
         <v>88</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D167" s="1" t="s">
         <v>14</v>
@@ -8781,12 +9909,18 @@
         <v>8</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G167" s="2">
-        <v>3</v>
-      </c>
-      <c r="H167" s="2">
+        <v>242</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H167" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I167" s="2">
+        <v>3</v>
+      </c>
+      <c r="J167" s="2">
         <v>1</v>
       </c>
     </row>
@@ -8798,7 +9932,7 @@
         <v>88</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D168" s="1" t="s">
         <v>14</v>
@@ -8807,12 +9941,18 @@
         <v>26</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G168" s="2">
-        <v>1</v>
-      </c>
-      <c r="H168" s="2">
+        <v>243</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H168" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I168" s="2">
+        <v>1</v>
+      </c>
+      <c r="J168" s="2">
         <v>2</v>
       </c>
     </row>
@@ -8824,7 +9964,7 @@
         <v>88</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>8</v>
@@ -8833,12 +9973,18 @@
         <v>26</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="G169" s="2">
-        <v>3</v>
-      </c>
-      <c r="H169" s="2">
+        <v>244</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H169" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I169" s="2">
+        <v>3</v>
+      </c>
+      <c r="J169" s="2">
         <v>0</v>
       </c>
     </row>
@@ -8850,7 +9996,7 @@
         <v>88</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>6</v>
@@ -8859,12 +10005,18 @@
         <v>18</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="G170" s="2">
-        <v>2</v>
-      </c>
-      <c r="H170" s="2">
+        <v>239</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H170" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I170" s="2">
+        <v>2</v>
+      </c>
+      <c r="J170" s="2">
         <v>2</v>
       </c>
     </row>
@@ -8876,7 +10028,7 @@
         <v>88</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>6</v>
@@ -8885,12 +10037,18 @@
         <v>20</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="G171" s="2">
-        <v>0</v>
-      </c>
-      <c r="H171" s="2">
+        <v>240</v>
+      </c>
+      <c r="G171" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H171" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I171" s="2">
+        <v>0</v>
+      </c>
+      <c r="J171" s="2">
         <v>3</v>
       </c>
     </row>
@@ -8902,7 +10060,7 @@
         <v>88</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D172" s="1" t="s">
         <v>6</v>
@@ -8911,12 +10069,18 @@
         <v>30</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="G172" s="2">
-        <v>2</v>
-      </c>
-      <c r="H172" s="2">
+        <v>241</v>
+      </c>
+      <c r="G172" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H172" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I172" s="2">
+        <v>2</v>
+      </c>
+      <c r="J172" s="2">
         <v>0</v>
       </c>
     </row>
@@ -8928,7 +10092,7 @@
         <v>88</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>18</v>
@@ -8937,12 +10101,18 @@
         <v>20</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G173" s="2">
-        <v>3</v>
-      </c>
-      <c r="H173" s="2">
+        <v>242</v>
+      </c>
+      <c r="G173" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H173" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I173" s="2">
+        <v>3</v>
+      </c>
+      <c r="J173" s="2">
         <v>1</v>
       </c>
     </row>
@@ -8954,7 +10124,7 @@
         <v>88</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>18</v>
@@ -8963,12 +10133,18 @@
         <v>30</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G174" s="2">
-        <v>1</v>
-      </c>
-      <c r="H174" s="2">
+        <v>243</v>
+      </c>
+      <c r="G174" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H174" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I174" s="2">
+        <v>1</v>
+      </c>
+      <c r="J174" s="2">
         <v>2</v>
       </c>
     </row>
@@ -8980,7 +10156,7 @@
         <v>88</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>20</v>
@@ -8989,12 +10165,18 @@
         <v>30</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="G175" s="2">
-        <v>3</v>
-      </c>
-      <c r="H175" s="2">
+        <v>244</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H175" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I175" s="2">
+        <v>3</v>
+      </c>
+      <c r="J175" s="2">
         <v>0</v>
       </c>
     </row>
@@ -9006,7 +10188,7 @@
         <v>88</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>16</v>
@@ -9015,12 +10197,18 @@
         <v>22</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="G176" s="2">
-        <v>2</v>
-      </c>
-      <c r="H176" s="2">
+        <v>239</v>
+      </c>
+      <c r="G176" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H176" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I176" s="2">
+        <v>2</v>
+      </c>
+      <c r="J176" s="2">
         <v>2</v>
       </c>
     </row>
@@ -9032,7 +10220,7 @@
         <v>88</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>16</v>
@@ -9041,12 +10229,18 @@
         <v>24</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="G177" s="2">
-        <v>0</v>
-      </c>
-      <c r="H177" s="2">
+        <v>240</v>
+      </c>
+      <c r="G177" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H177" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I177" s="2">
+        <v>0</v>
+      </c>
+      <c r="J177" s="2">
         <v>3</v>
       </c>
     </row>
@@ -9058,7 +10252,7 @@
         <v>88</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D178" s="1" t="s">
         <v>16</v>
@@ -9067,12 +10261,18 @@
         <v>28</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="G178" s="2">
-        <v>2</v>
-      </c>
-      <c r="H178" s="2">
+        <v>241</v>
+      </c>
+      <c r="G178" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H178" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I178" s="2">
+        <v>2</v>
+      </c>
+      <c r="J178" s="2">
         <v>0</v>
       </c>
     </row>
@@ -9084,7 +10284,7 @@
         <v>88</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>22</v>
@@ -9093,12 +10293,18 @@
         <v>24</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G179" s="2">
-        <v>3</v>
-      </c>
-      <c r="H179" s="2">
+        <v>242</v>
+      </c>
+      <c r="G179" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H179" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I179" s="2">
+        <v>3</v>
+      </c>
+      <c r="J179" s="2">
         <v>1</v>
       </c>
     </row>
@@ -9110,7 +10316,7 @@
         <v>88</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D180" s="1" t="s">
         <v>22</v>
@@ -9119,12 +10325,18 @@
         <v>28</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G180" s="2">
-        <v>1</v>
-      </c>
-      <c r="H180" s="2">
+        <v>243</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H180" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I180" s="2">
+        <v>1</v>
+      </c>
+      <c r="J180" s="2">
         <v>2</v>
       </c>
     </row>
@@ -9136,7 +10348,7 @@
         <v>88</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D181" s="1" t="s">
         <v>24</v>
@@ -9145,12 +10357,18 @@
         <v>28</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="G181" s="2">
-        <v>3</v>
-      </c>
-      <c r="H181" s="2">
+        <v>244</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H181" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I181" s="2">
+        <v>3</v>
+      </c>
+      <c r="J181" s="2">
         <v>0</v>
       </c>
     </row>
@@ -9162,7 +10380,7 @@
         <v>89</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D182" s="1" t="s">
         <v>2</v>
@@ -9171,12 +10389,18 @@
         <v>28</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="G182" s="2">
-        <v>1</v>
-      </c>
-      <c r="H182" s="2">
+        <v>245</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H182" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I182" s="2">
+        <v>1</v>
+      </c>
+      <c r="J182" s="2">
         <v>2</v>
       </c>
     </row>
@@ -9188,7 +10412,7 @@
         <v>89</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D183" s="1" t="s">
         <v>10</v>
@@ -9197,12 +10421,18 @@
         <v>24</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G183" s="2">
-        <v>2</v>
-      </c>
-      <c r="H183" s="2">
+        <v>246</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H183" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I183" s="2">
+        <v>2</v>
+      </c>
+      <c r="J183" s="2">
         <v>0</v>
       </c>
     </row>
@@ -9214,7 +10444,7 @@
         <v>89</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D184" s="1" t="s">
         <v>12</v>
@@ -9223,12 +10453,18 @@
         <v>22</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="G184" s="2">
-        <v>0</v>
-      </c>
-      <c r="H184" s="2">
+        <v>247</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H184" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I184" s="2">
+        <v>0</v>
+      </c>
+      <c r="J184" s="2">
         <v>1</v>
       </c>
     </row>
@@ -9240,7 +10476,7 @@
         <v>89</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D185" s="1" t="s">
         <v>32</v>
@@ -9249,12 +10485,18 @@
         <v>16</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G185" s="2">
-        <v>1</v>
-      </c>
-      <c r="H185" s="2">
+        <v>248</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H185" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I185" s="2">
+        <v>1</v>
+      </c>
+      <c r="J185" s="2">
         <v>2</v>
       </c>
     </row>
@@ -9266,7 +10508,7 @@
         <v>89</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D186" s="1" t="s">
         <v>4</v>
@@ -9275,12 +10517,18 @@
         <v>30</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="G186" s="2">
-        <v>2</v>
-      </c>
-      <c r="H186" s="2">
+        <v>249</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H186" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I186" s="2">
+        <v>2</v>
+      </c>
+      <c r="J186" s="2">
         <v>0</v>
       </c>
     </row>
@@ -9292,7 +10540,7 @@
         <v>89</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>14</v>
@@ -9301,12 +10549,18 @@
         <v>20</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="G187" s="2">
-        <v>0</v>
-      </c>
-      <c r="H187" s="2">
+        <v>250</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H187" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I187" s="2">
+        <v>0</v>
+      </c>
+      <c r="J187" s="2">
         <v>1</v>
       </c>
     </row>
@@ -9318,7 +10572,7 @@
         <v>89</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D188" s="1" t="s">
         <v>8</v>
@@ -9327,12 +10581,18 @@
         <v>18</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="G188" s="2">
-        <v>1</v>
-      </c>
-      <c r="H188" s="2">
+        <v>251</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="H188" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I188" s="2">
+        <v>1</v>
+      </c>
+      <c r="J188" s="2">
         <v>2</v>
       </c>
     </row>
@@ -9344,7 +10604,7 @@
         <v>89</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D189" s="1" t="s">
         <v>26</v>
@@ -9353,12 +10613,18 @@
         <v>6</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="G189" s="2">
-        <v>2</v>
-      </c>
-      <c r="H189" s="2">
+        <v>252</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H189" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="I189" s="2">
+        <v>2</v>
+      </c>
+      <c r="J189" s="2">
         <v>0</v>
       </c>
     </row>
@@ -9370,7 +10636,7 @@
         <v>90</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>2</v>
@@ -9379,12 +10645,18 @@
         <v>26</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="G190" s="2">
-        <v>2</v>
-      </c>
-      <c r="H190" s="2">
+        <v>253</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H190" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I190" s="2">
+        <v>2</v>
+      </c>
+      <c r="J190" s="2">
         <v>1</v>
       </c>
     </row>
@@ -9396,7 +10668,7 @@
         <v>90</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D191" s="1" t="s">
         <v>10</v>
@@ -9405,12 +10677,18 @@
         <v>8</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="G191" s="2">
-        <v>0</v>
-      </c>
-      <c r="H191" s="2">
+        <v>254</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H191" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="I191" s="2">
+        <v>0</v>
+      </c>
+      <c r="J191" s="2">
         <v>0</v>
       </c>
     </row>
@@ -9422,7 +10700,7 @@
         <v>90</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D192" s="1" t="s">
         <v>12</v>
@@ -9431,12 +10709,18 @@
         <v>14</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G192" s="2">
-        <v>1</v>
-      </c>
-      <c r="H192" s="2">
+        <v>255</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H192" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I192" s="2">
+        <v>1</v>
+      </c>
+      <c r="J192" s="2">
         <v>1</v>
       </c>
     </row>
@@ -9448,7 +10732,7 @@
         <v>90</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>32</v>
@@ -9457,12 +10741,18 @@
         <v>4</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="G193" s="2">
-        <v>2</v>
-      </c>
-      <c r="H193" s="2">
+        <v>256</v>
+      </c>
+      <c r="G193" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="H193" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="I193" s="2">
+        <v>2</v>
+      </c>
+      <c r="J193" s="2">
         <v>0</v>
       </c>
     </row>
@@ -9474,7 +10764,7 @@
         <v>91</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>2</v>
@@ -9483,12 +10773,18 @@
         <v>32</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="G194" s="2">
-        <v>1</v>
-      </c>
-      <c r="H194" s="2">
+        <v>257</v>
+      </c>
+      <c r="G194" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H194" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I194" s="2">
+        <v>1</v>
+      </c>
+      <c r="J194" s="2">
         <v>0</v>
       </c>
     </row>
@@ -9500,7 +10796,7 @@
         <v>91</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>10</v>
@@ -9509,12 +10805,18 @@
         <v>12</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="G195" s="2">
-        <v>0</v>
-      </c>
-      <c r="H195" s="2">
+        <v>258</v>
+      </c>
+      <c r="G195" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H195" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I195" s="2">
+        <v>0</v>
+      </c>
+      <c r="J195" s="2">
         <v>1</v>
       </c>
     </row>
@@ -9526,7 +10828,7 @@
         <v>92</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>2</v>
@@ -9535,12 +10837,18 @@
         <v>4</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="G196" s="2">
-        <v>2</v>
-      </c>
-      <c r="H196" s="2">
+        <v>259</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H196" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="I196" s="2">
+        <v>2</v>
+      </c>
+      <c r="J196" s="2">
         <v>1</v>
       </c>
     </row>
